--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2610,7 +2610,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2623,13 +2623,13 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>79</v>

--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/main/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
